--- a/Sets-DemoModels.xlsx
+++ b/Sets-DemoModels.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0EDA36A-90F4-4369-8133-940B574E8AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553530A7-8E3A-4EA3-BCA5-92432524CA11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{008F860A-1793-4F78-8899-BE3F7B7A437A}"/>
   </bookViews>
@@ -1458,7 +1458,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>72</v>
@@ -1550,7 +1550,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
         <v>81</v>
@@ -1573,7 +1573,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="B23" t="s">
         <v>72</v>
@@ -1596,7 +1596,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="B24" t="s">
         <v>81</v>

--- a/Sets-DemoModels.xlsx
+++ b/Sets-DemoModels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553530A7-8E3A-4EA3-BCA5-92432524CA11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42EEB976-72ED-406A-AA59-FE7F53C99304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{008F860A-1793-4F78-8899-BE3F7B7A437A}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
   <si>
     <t>~TFM_Psets</t>
   </si>
@@ -247,15 +247,9 @@
     <t>MANELC_TECH</t>
   </si>
   <si>
-    <t>PSET_MANELC_GRID</t>
-  </si>
-  <si>
     <t>Furnace</t>
   </si>
   <si>
-    <t>PSET_MANHEAT_GRID</t>
-  </si>
-  <si>
     <t>BIOBoiler</t>
   </si>
   <si>
@@ -280,9 +274,6 @@
     <t>ELCBoiler</t>
   </si>
   <si>
-    <t>PSET_MANHEAT_DECELC</t>
-  </si>
-  <si>
     <t>SOLELC</t>
   </si>
   <si>
@@ -296,6 +287,27 @@
   </si>
   <si>
     <t>WNDELC,SOLELC</t>
+  </si>
+  <si>
+    <t>ELCTHT</t>
+  </si>
+  <si>
+    <t>BHEAT</t>
+  </si>
+  <si>
+    <t>FHEAT</t>
+  </si>
+  <si>
+    <t>PSET_MANELC_ELC</t>
+  </si>
+  <si>
+    <t>PSET_PHEAT_ELC</t>
+  </si>
+  <si>
+    <t>PSET_BHEAT_ELC</t>
+  </si>
+  <si>
+    <t>PSET_MANHEAT_BHEAT</t>
   </si>
 </sst>
 </file>
@@ -787,11 +799,11 @@
     <row r="5" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6" t="s">
@@ -806,11 +818,11 @@
     <row r="6" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6" t="s">
@@ -1097,7 +1109,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="26.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="4"/>
+    <col min="5" max="5" width="13.21875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -1185,7 +1198,7 @@
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6" t="s">
@@ -1208,7 +1221,7 @@
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6" t="s">
@@ -1227,7 +1240,7 @@
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6" t="s">
@@ -1447,7 +1460,7 @@
         <v>46</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>13</v>
@@ -1461,16 +1474,16 @@
         <v>55</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>13</v>
@@ -1484,7 +1497,7 @@
         <v>64</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>41</v>
@@ -1493,7 +1506,7 @@
         <v>43</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>13</v>
@@ -1504,10 +1517,10 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>41</v>
@@ -1516,7 +1529,7 @@
         <v>43</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>13</v>
@@ -1530,7 +1543,7 @@
         <v>64</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>40</v>
@@ -1539,7 +1552,7 @@
         <v>43</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>13</v>
@@ -1553,16 +1566,16 @@
         <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>13</v>
@@ -1573,19 +1586,19 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>43</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>13</v>
@@ -1596,19 +1609,19 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>43</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>13</v>
